--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FunctionOpenProto" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>#</t>
   </si>
@@ -177,34 +177,10 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>背包</t>
-  </si>
-  <si>
-    <t>UIRoleEquip</t>
-  </si>
-  <si>
-    <t>转换职业</t>
-  </si>
-  <si>
-    <t>UIOccTwo</t>
-  </si>
-  <si>
-    <t>装备商店</t>
-  </si>
-  <si>
-    <t>UIStore</t>
-  </si>
-  <si>
-    <t>仓库</t>
-  </si>
-  <si>
-    <t>UIWarehouse</t>
-  </si>
-  <si>
-    <t>邮件</t>
-  </si>
-  <si>
-    <t>UIMail</t>
+    <t>长老</t>
+  </si>
+  <si>
+    <t>UIMedalExchange</t>
   </si>
 </sst>
 </file>
@@ -1370,104 +1346,40 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C7" s="2">
-        <v>1002</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1"/>
     <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C8" s="2">
-        <v>1003</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J8" s="2">
-        <v>0</v>
-      </c>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C9" s="2">
-        <v>1004</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J9" s="2">
-        <v>0</v>
-      </c>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C10" s="2">
-        <v>1005</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2">
-        <v>-1</v>
-      </c>
-      <c r="J10" s="2">
-        <v>0</v>
-      </c>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>

--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -180,7 +180,7 @@
     <t>长老</t>
   </si>
   <si>
-    <t>UIMedalExchange</t>
+    <t>WindowID_MedalExchange</t>
   </si>
 </sst>
 </file>
@@ -1194,7 +1194,7 @@
     <col min="2" max="2" width="12.75" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="4" customWidth="1"/>
     <col min="4" max="4" width="15.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15" style="4" customWidth="1"/>
+    <col min="5" max="5" width="37" style="4" customWidth="1"/>
     <col min="6" max="6" width="16.5" style="4" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="22.75" style="4" customWidth="1"/>
